--- a/integrations/google-sheets/Viet-Dataverse-Google-Sheets-Template.xlsx
+++ b/integrations/google-sheets/Viet-Dataverse-Google-Sheets-Template.xlsx
@@ -109,15 +109,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -197,6 +198,1534 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vàng SJC</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vàng SJC'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Vàng SJC'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vàng SJC'!$B$2:$B$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Vàng SJC'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Vàng SJC'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vàng SJC'!$C$2:$C$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>VND/lượng</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Bạc</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Bạc'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Bạc'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Bạc'!$B$2:$B$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Bạc'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Bạc'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Bạc'!$C$2:$C$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>VND/lượng</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Lãi suất LNH</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Lãi suất LNH'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Lãi suất LNH'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lãi suất LNH'!$B$2:$B$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Lãi suất LNH'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Lãi suất LNH'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lãi suất LNH'!$C$2:$C$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Lãi suất LNH'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Lãi suất LNH'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lãi suất LNH'!$D$2:$D$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Lãi suất LNH'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Lãi suất LNH'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lãi suất LNH'!$E$2:$E$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Lãi suất LNH'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Lãi suất LNH'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lãi suất LNH'!$F$2:$F$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>%/năm</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Tỷ giá</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Tỷ giá'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Tỷ giá'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Tỷ giá'!$B$2:$B$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>VND/USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Tiền gửi ACB</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Tiền gửi ACB'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Tiền gửi ACB'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Tiền gửi ACB'!$B$2:$B$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Tiền gửi ACB'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Tiền gửi ACB'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Tiền gửi ACB'!$C$2:$C$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Tiền gửi ACB'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Tiền gửi ACB'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Tiền gửi ACB'!$D$2:$D$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Tiền gửi ACB'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Tiền gửi ACB'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Tiền gửi ACB'!$E$2:$E$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Tiền gửi ACB'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Tiền gửi ACB'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Tiền gửi ACB'!$F$2:$F$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>%/năm</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Thế giới</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Thế giới'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Thế giới'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Thế giới'!$B$2:$B$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Thế giới'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Thế giới'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Thế giới'!$C$2:$C$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Thế giới'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Thế giới'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Thế giới'!$D$2:$D$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>CPI</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'CPI'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'CPI'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'CPI'!$B$2:$B$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'CPI'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'CPI'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'CPI'!$C$2:$C$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>%</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Xuất nhập khẩu</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Xuất nhập khẩu'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Xuất nhập khẩu'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Xuất nhập khẩu'!$B$2:$B$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Xuất nhập khẩu'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Xuất nhập khẩu'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Xuất nhập khẩu'!$C$2:$C$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Xuất nhập khẩu'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Xuất nhập khẩu'!$A$2:$A$400</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Xuất nhập khẩu'!$D$2:$D$400</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>tỷ USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -488,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C12"/>
+  <dimension ref="B2:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -510,90 +2039,100 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>CHỈ CÓ MỘT BƯỚC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Dán API key của bạn vào ô bên phải  →</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
+      <c r="C6" s="5" t="n"/>
     </row>
-    <row r="5">
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>CHỈ CÓ MỘT BƯỚC</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Xong.</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Chín tab bên dưới tự đổ dữ liệu ngay. Không cần cấp quyền, không cài gì.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có key?</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Lấy miễn phí tại https://vietdataverse.online/pages/developer.html</t>
-        </is>
+          <t>Làm mới toàn bộ 9 tab</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Làm mới dữ liệu</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Google tự làm mới khi bạn mở file. Muốn ép ngay: menu Xem → làm mới, hoặc F5.</t>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Xong.</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Chín tab bên dưới tự đổ dữ liệu ngay. Không cần cấp quyền, không cài gì.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Đổi khoảng thời gian</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Sửa period=1y trong công thức ở ô A1 của tab bất kỳ (7d, 1m, 1y, all).</t>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Chưa có key?</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Lấy miễn phí tại https://vietdataverse.online/pages/developer.html</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Hạn mức</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Mỗi tab là một lượt gọi API. Gói miễn phí 2 lượt/tháng chỉ đủ để thử; mở file thường xuyên thì cần gói trả phí.</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Làm mới ngay</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Tăng số trong ô C7 lên 1 đơn vị (1 → 2 → 3…). Cả 9 tab tải lại cùng lúc. Tải lại trang KHÔNG làm mới — Google giữ cache ~1 giờ.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Đổi khoảng thời gian</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Sửa period=1y trong công thức ở ô A1 của tab bất kỳ (7d, 1m, 1y, all).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Hạn mức</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Mỗi tab là một lượt gọi API (9 tab = 9 lượt mỗi lần mở). Gói miễn phí 20 lượt/tháng; mở file thường xuyên thì cần gói trả phí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Bảo mật</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Key nằm trong ô C4 của bản copy của bạn. Đừng chia sẻ file này cho người lạ.</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Key nằm trong ô C6 của bản copy của bạn. Đừng chia sẻ file này cho người lạ.</t>
         </is>
       </c>
     </row>
@@ -623,10 +2162,10 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IF('Bắt đầu'!$C$4="","← Dán API key vào ô C4 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/macro/trade?months=24&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$4))</f>
+        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/macro/trade?months=24&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
         <v/>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Kim ngạch xuất nhập khẩu theo tháng</t>
         </is>
@@ -634,6 +2173,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -658,10 +2198,10 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IF('Bắt đầu'!$C$4="","← Dán API key vào ô C4 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/gold?period=1y&amp;type=SJC&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$4))</f>
+        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/gold?period=1y&amp;type=SJC&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
         <v/>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Giá vàng SJC mua vào / bán ra theo ngày</t>
         </is>
@@ -669,6 +2209,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -693,10 +2234,10 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IF('Bắt đầu'!$C$4="","← Dán API key vào ô C4 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/silver?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$4))</f>
+        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/silver?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
         <v/>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Giá bạc Phú Quý theo ngày</t>
         </is>
@@ -704,6 +2245,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -728,10 +2270,10 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IF('Bắt đầu'!$C$4="","← Dán API key vào ô C4 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/sbv-interbank?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$4))</f>
+        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/sbv-interbank?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
         <v/>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Lãi suất liên ngân hàng + lãi suất điều hành SBV</t>
         </is>
@@ -739,6 +2281,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -763,10 +2306,10 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IF('Bắt đầu'!$C$4="","← Dán API key vào ô C4 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/sbv-rate?period=1y&amp;bank=SBV&amp;currency=USD&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$4))</f>
+        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/sbv-rate?period=1y&amp;bank=SBV&amp;currency=USD&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
         <v/>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Tỷ giá trung tâm USD/VND</t>
         </is>
@@ -774,6 +2317,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -798,10 +2342,10 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IF('Bắt đầu'!$C$4="","← Dán API key vào ô C4 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/termdepo?period=1y&amp;bank=ACB&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$4))</f>
+        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/termdepo?period=1y&amp;bank=ACB&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
         <v/>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Lãi suất tiền gửi theo kỳ hạn</t>
         </is>
@@ -809,6 +2353,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -833,10 +2378,10 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IF('Bắt đầu'!$C$4="","← Dán API key vào ô C4 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/global-macro?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$4))</f>
+        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/global-macro?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
         <v/>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Vàng, bạc, NASDAQ thế giới</t>
         </is>
@@ -844,6 +2389,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -868,10 +2414,10 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IF('Bắt đầu'!$C$4="","← Dán API key vào ô C4 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/macro/cpi?view=monthly&amp;years=5&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$4))</f>
+        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/macro/cpi?view=monthly&amp;years=5&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
         <v/>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Chỉ số giá tiêu dùng theo tháng</t>
         </is>
@@ -879,6 +2425,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -903,10 +2450,10 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IF('Bắt đầu'!$C$4="","← Dán API key vào ô C4 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/macro/gdp?format=csv&amp;api_key="&amp;'Bắt đầu'!$C$4))</f>
+        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/macro/gdp?format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
         <v/>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>GDP theo quý và khu vực</t>
         </is>

--- a/integrations/google-sheets/Viet-Dataverse-Google-Sheets-Template.xlsx
+++ b/integrations/google-sheets/Viet-Dataverse-Google-Sheets-Template.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CPI" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GDP" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Xuất nhập khẩu" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_dữ liệu thô" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,12 +61,27 @@
       <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00141413"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002F5FDE"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <i val="1"/>
       <color rgb="005E5D59"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +96,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5FDE"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,21 +130,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -227,7 +248,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Vàng SJC'!B1</f>
+              <f>'Vàng SJC'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -245,12 +266,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Vàng SJC'!$A$2:$A$400</f>
+              <f>'Vàng SJC'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vàng SJC'!$B$2:$B$400</f>
+              <f>'Vàng SJC'!$B$4:$B$2000</f>
             </numRef>
           </val>
         </ser>
@@ -259,7 +280,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Vàng SJC'!C1</f>
+              <f>'Vàng SJC'!C3</f>
             </strRef>
           </tx>
           <spPr>
@@ -277,12 +298,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Vàng SJC'!$A$2:$A$400</f>
+              <f>'Vàng SJC'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vàng SJC'!$C$2:$C$400</f>
+              <f>'Vàng SJC'!$C$4:$C$2000</f>
             </numRef>
           </val>
         </ser>
@@ -363,7 +384,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Bạc'!B1</f>
+              <f>'Bạc'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -381,12 +402,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Bạc'!$A$2:$A$400</f>
+              <f>'Bạc'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Bạc'!$B$2:$B$400</f>
+              <f>'Bạc'!$B$4:$B$2000</f>
             </numRef>
           </val>
         </ser>
@@ -395,7 +416,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Bạc'!C1</f>
+              <f>'Bạc'!C3</f>
             </strRef>
           </tx>
           <spPr>
@@ -413,12 +434,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Bạc'!$A$2:$A$400</f>
+              <f>'Bạc'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Bạc'!$C$2:$C$400</f>
+              <f>'Bạc'!$C$4:$C$2000</f>
             </numRef>
           </val>
         </ser>
@@ -499,7 +520,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Lãi suất LNH'!B1</f>
+              <f>'Lãi suất LNH'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -517,12 +538,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lãi suất LNH'!$A$2:$A$400</f>
+              <f>'Lãi suất LNH'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lãi suất LNH'!$B$2:$B$400</f>
+              <f>'Lãi suất LNH'!$B$4:$B$2000</f>
             </numRef>
           </val>
         </ser>
@@ -531,7 +552,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Lãi suất LNH'!C1</f>
+              <f>'Lãi suất LNH'!C3</f>
             </strRef>
           </tx>
           <spPr>
@@ -549,12 +570,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lãi suất LNH'!$A$2:$A$400</f>
+              <f>'Lãi suất LNH'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lãi suất LNH'!$C$2:$C$400</f>
+              <f>'Lãi suất LNH'!$C$4:$C$2000</f>
             </numRef>
           </val>
         </ser>
@@ -563,7 +584,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Lãi suất LNH'!D1</f>
+              <f>'Lãi suất LNH'!D3</f>
             </strRef>
           </tx>
           <spPr>
@@ -581,12 +602,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lãi suất LNH'!$A$2:$A$400</f>
+              <f>'Lãi suất LNH'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lãi suất LNH'!$D$2:$D$400</f>
+              <f>'Lãi suất LNH'!$D$4:$D$2000</f>
             </numRef>
           </val>
         </ser>
@@ -595,7 +616,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Lãi suất LNH'!E1</f>
+              <f>'Lãi suất LNH'!E3</f>
             </strRef>
           </tx>
           <spPr>
@@ -613,12 +634,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lãi suất LNH'!$A$2:$A$400</f>
+              <f>'Lãi suất LNH'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lãi suất LNH'!$E$2:$E$400</f>
+              <f>'Lãi suất LNH'!$E$4:$E$2000</f>
             </numRef>
           </val>
         </ser>
@@ -627,7 +648,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Lãi suất LNH'!F1</f>
+              <f>'Lãi suất LNH'!F3</f>
             </strRef>
           </tx>
           <spPr>
@@ -645,12 +666,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lãi suất LNH'!$A$2:$A$400</f>
+              <f>'Lãi suất LNH'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lãi suất LNH'!$F$2:$F$400</f>
+              <f>'Lãi suất LNH'!$F$4:$F$2000</f>
             </numRef>
           </val>
         </ser>
@@ -731,7 +752,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Tỷ giá'!B1</f>
+              <f>'Tỷ giá'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -749,12 +770,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Tỷ giá'!$A$2:$A$400</f>
+              <f>'Tỷ giá'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tỷ giá'!$B$2:$B$400</f>
+              <f>'Tỷ giá'!$B$4:$B$2000</f>
             </numRef>
           </val>
         </ser>
@@ -835,7 +856,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Tiền gửi ACB'!B1</f>
+              <f>'Tiền gửi ACB'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -853,12 +874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Tiền gửi ACB'!$A$2:$A$400</f>
+              <f>'Tiền gửi ACB'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tiền gửi ACB'!$B$2:$B$400</f>
+              <f>'Tiền gửi ACB'!$B$4:$B$2000</f>
             </numRef>
           </val>
         </ser>
@@ -867,7 +888,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Tiền gửi ACB'!C1</f>
+              <f>'Tiền gửi ACB'!C3</f>
             </strRef>
           </tx>
           <spPr>
@@ -885,12 +906,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Tiền gửi ACB'!$A$2:$A$400</f>
+              <f>'Tiền gửi ACB'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tiền gửi ACB'!$C$2:$C$400</f>
+              <f>'Tiền gửi ACB'!$C$4:$C$2000</f>
             </numRef>
           </val>
         </ser>
@@ -899,7 +920,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Tiền gửi ACB'!D1</f>
+              <f>'Tiền gửi ACB'!D3</f>
             </strRef>
           </tx>
           <spPr>
@@ -917,12 +938,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Tiền gửi ACB'!$A$2:$A$400</f>
+              <f>'Tiền gửi ACB'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tiền gửi ACB'!$D$2:$D$400</f>
+              <f>'Tiền gửi ACB'!$D$4:$D$2000</f>
             </numRef>
           </val>
         </ser>
@@ -931,7 +952,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Tiền gửi ACB'!E1</f>
+              <f>'Tiền gửi ACB'!E3</f>
             </strRef>
           </tx>
           <spPr>
@@ -949,12 +970,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Tiền gửi ACB'!$A$2:$A$400</f>
+              <f>'Tiền gửi ACB'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tiền gửi ACB'!$E$2:$E$400</f>
+              <f>'Tiền gửi ACB'!$E$4:$E$2000</f>
             </numRef>
           </val>
         </ser>
@@ -963,7 +984,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Tiền gửi ACB'!F1</f>
+              <f>'Tiền gửi ACB'!F3</f>
             </strRef>
           </tx>
           <spPr>
@@ -981,12 +1002,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Tiền gửi ACB'!$A$2:$A$400</f>
+              <f>'Tiền gửi ACB'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tiền gửi ACB'!$F$2:$F$400</f>
+              <f>'Tiền gửi ACB'!$F$4:$F$2000</f>
             </numRef>
           </val>
         </ser>
@@ -1067,7 +1088,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Thế giới'!B1</f>
+              <f>'Thế giới'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -1085,12 +1106,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Thế giới'!$A$2:$A$400</f>
+              <f>'Thế giới'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Thế giới'!$B$2:$B$400</f>
+              <f>'Thế giới'!$B$4:$B$2000</f>
             </numRef>
           </val>
         </ser>
@@ -1099,7 +1120,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Thế giới'!C1</f>
+              <f>'Thế giới'!C3</f>
             </strRef>
           </tx>
           <spPr>
@@ -1117,12 +1138,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Thế giới'!$A$2:$A$400</f>
+              <f>'Thế giới'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Thế giới'!$C$2:$C$400</f>
+              <f>'Thế giới'!$C$4:$C$2000</f>
             </numRef>
           </val>
         </ser>
@@ -1131,7 +1152,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Thế giới'!D1</f>
+              <f>'Thế giới'!D3</f>
             </strRef>
           </tx>
           <spPr>
@@ -1149,12 +1170,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Thế giới'!$A$2:$A$400</f>
+              <f>'Thế giới'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Thế giới'!$D$2:$D$400</f>
+              <f>'Thế giới'!$D$4:$D$2000</f>
             </numRef>
           </val>
         </ser>
@@ -1235,7 +1256,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'CPI'!B1</f>
+              <f>'CPI'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -1253,12 +1274,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'CPI'!$A$2:$A$400</f>
+              <f>'CPI'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'CPI'!$B$2:$B$400</f>
+              <f>'CPI'!$B$4:$B$2000</f>
             </numRef>
           </val>
         </ser>
@@ -1267,7 +1288,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'CPI'!C1</f>
+              <f>'CPI'!C3</f>
             </strRef>
           </tx>
           <spPr>
@@ -1285,12 +1306,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'CPI'!$A$2:$A$400</f>
+              <f>'CPI'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'CPI'!$C$2:$C$400</f>
+              <f>'CPI'!$C$4:$C$2000</f>
             </numRef>
           </val>
         </ser>
@@ -1371,7 +1392,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Xuất nhập khẩu'!B1</f>
+              <f>'Xuất nhập khẩu'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -1389,12 +1410,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Xuất nhập khẩu'!$A$2:$A$400</f>
+              <f>'Xuất nhập khẩu'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Xuất nhập khẩu'!$B$2:$B$400</f>
+              <f>'Xuất nhập khẩu'!$B$4:$B$2000</f>
             </numRef>
           </val>
         </ser>
@@ -1403,7 +1424,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Xuất nhập khẩu'!C1</f>
+              <f>'Xuất nhập khẩu'!C3</f>
             </strRef>
           </tx>
           <spPr>
@@ -1421,12 +1442,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Xuất nhập khẩu'!$A$2:$A$400</f>
+              <f>'Xuất nhập khẩu'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Xuất nhập khẩu'!$C$2:$C$400</f>
+              <f>'Xuất nhập khẩu'!$C$4:$C$2000</f>
             </numRef>
           </val>
         </ser>
@@ -1435,7 +1456,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Xuất nhập khẩu'!D1</f>
+              <f>'Xuất nhập khẩu'!D3</f>
             </strRef>
           </tx>
           <spPr>
@@ -1453,12 +1474,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Xuất nhập khẩu'!$A$2:$A$400</f>
+              <f>'Xuất nhập khẩu'!$A$4:$A$2000</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Xuất nhập khẩu'!$D$2:$D$400</f>
+              <f>'Xuất nhập khẩu'!$D$4:$D$2000</f>
             </numRef>
           </val>
         </ser>
@@ -1516,9 +1537,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="2880000"/>
@@ -1543,9 +1564,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="2880000"/>
@@ -1570,9 +1591,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="2880000"/>
@@ -1597,9 +1618,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="2880000"/>
@@ -1624,9 +1645,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="2880000"/>
@@ -1651,9 +1672,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="2880000"/>
@@ -1678,9 +1699,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="2880000"/>
@@ -1705,9 +1726,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="2880000"/>
@@ -2021,8 +2042,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -2035,7 +2056,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Chín bộ dữ liệu vĩ mô &amp; thị trường Việt Nam, cập nhật tự động.</t>
+          <t>Chín bộ dữ liệu vĩ mô &amp; thị trường Việt Nam.</t>
         </is>
       </c>
     </row>
@@ -2055,82 +2076,82 @@
       <c r="C6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Làm mới toàn bộ 9 tab</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Làm mới ngay</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Xong.</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Chín tab bên dưới tự đổ dữ liệu ngay. Không cần cấp quyền, không cài gì.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Chín tab bên dưới tự đổ dữ liệu, mỗi tab có biểu đồ và ngày dữ liệu mới nhất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Chưa có key?</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Lấy miễn phí tại https://vietdataverse.online/pages/developer.html</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Làm mới ngay</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Tăng số trong ô C7 lên 1 đơn vị (1 → 2 → 3…). Cả 9 tab tải lại cùng lúc. Tải lại trang KHÔNG làm mới — Google giữ cache ~1 giờ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="7" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Làm mới</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Tăng số ở ô C7 (1 → 2 → 3…). Tải lại trang KHÔNG làm mới — Google giữ cache ~1 giờ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Hạn mức</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Cả file chỉ tốn 1 lượt API mỗi lần làm mới (không phải 9). Miễn phí 20 lượt/tháng; gói trả phí 1.000 lượt/tháng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Đổi khoảng thời gian</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Sửa period=1y trong công thức ở ô A1 của tab bất kỳ (7d, 1m, 1y, all).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Hạn mức</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Mỗi tab là một lượt gọi API (9 tab = 9 lượt mỗi lần mở). Gói miễn phí 20 lượt/tháng; mở file thường xuyên thì cần gói trả phí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Sửa period=1y trong công thức ô A1 của tab "_dữ liệu thô" (7d, 1m, 1y, all).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Bảo mật</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Key nằm trong ô C6 của bản copy của bạn. Đừng chia sẻ file này cho người lạ.</t>
         </is>
@@ -2147,33 +2168,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Dữ liệu mới nhất:</t>
+        </is>
+      </c>
+      <c r="B1" s="9">
+        <f>IFERROR(INDEX(SORT(FILTER(A4:A, A4:A&lt;&gt;""), 1, FALSE), 1), "—")</f>
+        <v/>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>(ngày/kỳ gần nhất có trong bộ này)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Kỳ</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Xuất (tỷ USD)</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Nhập (tỷ USD)</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Cán cân</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>XK cùng kỳ (%)</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>NK cùng kỳ (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6, Col7 where Col1 = 'trade'", 0), "")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/macro/trade?months=24&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
+        <f>IF('Bắt đầu'!$C$6="","Dán API key vào ô C6 của tab Bắt đầu",IFERROR(IMPORTDATA("https://api.vietdataverse.online/api/v1/excel/refresh-data?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6),"Không lấy được dữ liệu. Thường là đã hết lượt API của tháng — nâng gói tại https://vietdataverse.online/pages/pricing.html (hạn mức mới có hiệu lực ngay), hoặc kiểm tra lại API key ở ô C6."))</f>
         <v/>
       </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>Kim ngạch xuất nhập khẩu theo tháng</t>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>Tab kỹ thuật — đừng sửa. Đây là lượt gọi API DUY NHẤT của cả file; chín tab kia đọc lại từ đây bằng QUERY nên không tốn thêm lượt nào.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2183,28 +2273,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1">
-        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/gold?period=1y&amp;type=SJC&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Dữ liệu mới nhất:</t>
+        </is>
+      </c>
+      <c r="B1" s="9">
+        <f>IFERROR(INDEX(SORT(FILTER(A4:A, A4:A&lt;&gt;""), 1, FALSE), 1), "—")</f>
         <v/>
       </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>Giá vàng SJC mua vào / bán ra theo ngày</t>
-        </is>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>(ngày/kỳ gần nhất có trong bộ này)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Giá mua</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Giá bán</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4 where Col1 = 'gold'", 0), "")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2219,28 +2332,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1">
-        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/silver?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Dữ liệu mới nhất:</t>
+        </is>
+      </c>
+      <c r="B1" s="9">
+        <f>IFERROR(INDEX(SORT(FILTER(A4:A, A4:A&lt;&gt;""), 1, FALSE), 1), "—")</f>
         <v/>
       </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>Giá bạc Phú Quý theo ngày</t>
-        </is>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>(ngày/kỳ gần nhất có trong bộ này)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Giá mua</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Giá bán</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4 where Col1 = 'silver'", 0), "")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2255,28 +2391,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1">
-        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/sbv-interbank?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Dữ liệu mới nhất:</t>
+        </is>
+      </c>
+      <c r="B1" s="9">
+        <f>IFERROR(INDEX(SORT(FILTER(A4:A, A4:A&lt;&gt;""), 1, FALSE), 1), "—")</f>
         <v/>
       </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>Lãi suất liên ngân hàng + lãi suất điều hành SBV</t>
-        </is>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>(ngày/kỳ gần nhất có trong bộ này)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Qua đêm</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>1 tháng</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>3 tháng</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>6 tháng</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>9 tháng</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Chiết khấu</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Tái cấp vốn</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6, Col7, Col8, Col9 where Col1 = 'interbank'", 0), "")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2291,28 +2480,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1">
-        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/sbv-rate?period=1y&amp;bank=SBV&amp;currency=USD&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Dữ liệu mới nhất:</t>
+        </is>
+      </c>
+      <c r="B1" s="9">
+        <f>IFERROR(INDEX(SORT(FILTER(A4:A, A4:A&lt;&gt;""), 1, FALSE), 1), "—")</f>
         <v/>
       </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>Tỷ giá trung tâm USD/VND</t>
-        </is>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>(ngày/kỳ gần nhất có trong bộ này)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Tỷ giá trung tâm</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Mua tiền mặt</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Bán</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5 where Col1 = 'fx'", 0), "")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2327,28 +2545,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1">
-        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/termdepo?period=1y&amp;bank=ACB&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Dữ liệu mới nhất:</t>
+        </is>
+      </c>
+      <c r="B1" s="9">
+        <f>IFERROR(INDEX(SORT(FILTER(A4:A, A4:A&lt;&gt;""), 1, FALSE), 1), "—")</f>
         <v/>
       </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>Lãi suất tiền gửi theo kỳ hạn</t>
-        </is>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>(ngày/kỳ gần nhất có trong bộ này)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>1 tháng</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>3 tháng</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>6 tháng</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>12 tháng</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6, Col7 where Col1 = 'deposit'", 0), "")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2363,28 +2622,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1">
-        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/global-macro?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Dữ liệu mới nhất:</t>
+        </is>
+      </c>
+      <c r="B1" s="9">
+        <f>IFERROR(INDEX(SORT(FILTER(A4:A, A4:A&lt;&gt;""), 1, FALSE), 1), "—")</f>
         <v/>
       </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>Vàng, bạc, NASDAQ thế giới</t>
-        </is>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>(ngày/kỳ gần nhất có trong bộ này)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Vàng (USD/oz)</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Bạc (USD/oz)</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5 where Col1 = 'global'", 0), "")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2399,28 +2687,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1">
-        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/macro/cpi?view=monthly&amp;years=5&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Dữ liệu mới nhất:</t>
+        </is>
+      </c>
+      <c r="B1" s="9">
+        <f>IFERROR(INDEX(SORT(FILTER(A4:A, A4:A&lt;&gt;""), 1, FALSE), 1), "—")</f>
         <v/>
       </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>Chỉ số giá tiêu dùng theo tháng</t>
-        </is>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>(ngày/kỳ gần nhất có trong bộ này)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Kỳ</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>So tháng trước (%)</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>So cùng kỳ (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4 where Col1 = 'cpi'", 0), "")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2435,28 +2746,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1">
-        <f>IF('Bắt đầu'!$C$6="","← Dán API key vào ô C6 của tab Bắt đầu để đổ dữ liệu",IMPORTDATA("https://api.vietdataverse.online/api/v1/macro/gdp?format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7))</f>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Dữ liệu mới nhất:</t>
+        </is>
+      </c>
+      <c r="B1" s="9">
+        <f>IFERROR(INDEX(SORT(FILTER(A4:A, A4:A&lt;&gt;""), 1, FALSE), 1), "—")</f>
         <v/>
       </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>GDP theo quý và khu vực</t>
-        </is>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>(ngày/kỳ gần nhất có trong bộ này)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Năm</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Quý</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Khu vực</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>GDP (tỷ VND)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Tăng trưởng (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6 where Col1 = 'gdp'", 0), "")</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/integrations/google-sheets/Viet-Dataverse-Google-Sheets-Template.xlsx
+++ b/integrations/google-sheets/Viet-Dataverse-Google-Sheets-Template.xlsx
@@ -2235,7 +2235,7 @@
     </row>
     <row r="4">
       <c r="A4" s="13">
-        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6, Col7 where Col1 = 'trade'", 0), "")</f>
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6, Col7 where Col1 = 'trade'", 0), IF('_dữ liệu thô'!A1="dataset", "", '_dữ liệu thô'!A1))</f>
         <v/>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IF('Bắt đầu'!$C$6="","Dán API key vào ô C6 của tab Bắt đầu",IFERROR(IMPORTDATA("https://api.vietdataverse.online/api/v1/excel/refresh-data?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6, ",", "en_US"),"Không lấy được dữ liệu. Thường là đã hết lượt API của tháng — nâng gói tại https://vietdataverse.online/pages/pricing.html (hạn mức mới có hiệu lực ngay), hoặc kiểm tra lại API key ở ô C6."))</f>
+        <f>IF('Bắt đầu'!$C$6="","Dán API key vào ô C6 của tab Bắt đầu",IFERROR(IMPORTDATA("https://api.vietdataverse.online/api/v1/excel/refresh-data?period=1y&amp;format=csv&amp;api_key="&amp;'Bắt đầu'!$C$6&amp;"&amp;_r="&amp;'Bắt đầu'!$C$7, ",", "en_US"),"Không lấy được dữ liệu. Thường là đã hết lượt API của tháng — nâng gói tại https://vietdataverse.online/pages/pricing.html (hạn mức mới có hiệu lực ngay), hoặc kiểm tra lại API key ở ô C6."))</f>
         <v/>
       </c>
       <c r="K1" s="10" t="inlineStr">
@@ -8310,7 +8310,7 @@
     </row>
     <row r="4">
       <c r="A4" s="12">
-        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4 where Col1 = 'gold'", 0), "")</f>
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4 where Col1 = 'gold'", 0), IF('_dữ liệu thô'!A1="dataset", "", '_dữ liệu thô'!A1))</f>
         <v/>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
     </row>
     <row r="4">
       <c r="A4" s="12">
-        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4 where Col1 = 'silver'", 0), "")</f>
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4 where Col1 = 'silver'", 0), IF('_dữ liệu thô'!A1="dataset", "", '_dữ liệu thô'!A1))</f>
         <v/>
       </c>
     </row>
@@ -20434,7 +20434,7 @@
     </row>
     <row r="4">
       <c r="A4" s="12">
-        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6, Col7, Col8, Col9 where Col1 = 'interbank'", 0), "")</f>
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6, Col7, Col8, Col9 where Col1 = 'interbank'", 0), IF('_dữ liệu thô'!A1="dataset", "", '_dữ liệu thô'!A1))</f>
         <v/>
       </c>
     </row>
@@ -26487,7 +26487,7 @@
     </row>
     <row r="4">
       <c r="A4" s="12">
-        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5 where Col1 = 'fx'", 0), "")</f>
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5 where Col1 = 'fx'", 0), IF('_dữ liệu thô'!A1="dataset", "", '_dữ liệu thô'!A1))</f>
         <v/>
       </c>
     </row>
@@ -32552,7 +32552,7 @@
     </row>
     <row r="4">
       <c r="A4" s="12">
-        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6, Col7 where Col1 = 'deposit'", 0), "")</f>
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6, Col7 where Col1 = 'deposit'", 0), IF('_dữ liệu thô'!A1="dataset", "", '_dữ liệu thô'!A1))</f>
         <v/>
       </c>
     </row>
@@ -38605,7 +38605,7 @@
     </row>
     <row r="4">
       <c r="A4" s="12">
-        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5 where Col1 = 'global'", 0), "")</f>
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5 where Col1 = 'global'", 0), IF('_dữ liệu thô'!A1="dataset", "", '_dữ liệu thô'!A1))</f>
         <v/>
       </c>
     </row>
@@ -44652,7 +44652,7 @@
     </row>
     <row r="4">
       <c r="A4" s="13">
-        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4 where Col1 = 'cpi'", 0), "")</f>
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4 where Col1 = 'cpi'", 0), IF('_dữ liệu thô'!A1="dataset", "", '_dữ liệu thô'!A1))</f>
         <v/>
       </c>
     </row>
@@ -50711,7 +50711,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14">
-        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6 where Col1 = 'gdp'", 0), "")</f>
+        <f>IFERROR(QUERY('_dữ liệu thô'!A:I, "select Col2, Col3, Col4, Col5, Col6 where Col1 = 'gdp'", 0), IF('_dữ liệu thô'!A1="dataset", "", '_dữ liệu thô'!A1))</f>
         <v/>
       </c>
     </row>

--- a/integrations/google-sheets/Viet-Dataverse-Google-Sheets-Template.xlsx
+++ b/integrations/google-sheets/Viet-Dataverse-Google-Sheets-Template.xlsx
@@ -195,7 +195,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -607,11 +609,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C15"/>
+  <dimension ref="B2:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -674,65 +676,77 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Mở tab "Tổng quan" để xem bảng tổng quan; chín tab sau là dữ liệu chi tiết, mỗi tab có biểu đồ.</t>
+          <t>Mở tab "Tổng quan" để xem bảng tổng quan; chín tab sau là dữ liệu chi tiết, biểu đồ nằm ở tab Tổng quan.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Chưa có key?</t>
+          <t>Thấy thanh vàng?</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Lấy miễn phí tại https://vietdataverse.online/pages/developer.html</t>
+          <t>Sheets hỏi "Allow access" / "Cho phép truy cập" ở đầu trang: bấm cho phép, nếu không file không lấy được dữ liệu.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Làm mới</t>
+          <t>Chưa có key?</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Tăng số ở ô C7 (1 → 2 → 3…). Tải lại trang KHÔNG làm mới — Google giữ cache ~1 giờ.</t>
+          <t>Lấy miễn phí tại https://vietdataverse.online/pages/developer.html</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Khoảng thời gian</t>
+          <t>Làm mới</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Chọn ở ô C8: 1m (1 tháng), 1y (1 năm), all (toàn bộ lịch sử).</t>
+          <t>Tăng số ở ô C7 (1 → 2 → 3…). Tải lại trang KHÔNG làm mới — Google giữ cache ~1 giờ.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Hạn mức</t>
+          <t>Khoảng thời gian</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Cả file chỉ tốn 1 lượt API mỗi lần làm mới (không phải 9). Miễn phí 20 lượt/tháng; gói trả phí 1.000 lượt/tháng.</t>
+          <t>Chọn ở ô C8: 1m (1 tháng), 1y (1 năm), all (toàn bộ lịch sử).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>Hạn mức</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Cả file chỉ tốn 1 lượt API mỗi lần làm mới (không phải 9). Miễn phí 20 lượt/tháng; gói trả phí 1.000 lượt/tháng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
           <t>Bảo mật</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Key nằm trong ô C6 của bản copy của bạn. Đừng chia sẻ file này cho người lạ.</t>
         </is>
@@ -759,7 +773,7 @@
   <cols>
     <col width="13" customWidth="1" style="30" min="1" max="1"/>
     <col width="13" customWidth="1" style="30" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" style="27" min="4" max="4"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -779,7 +793,7 @@
         </is>
       </c>
       <c r="B2" s="25">
-        <f>IF(VDV_STATUS&lt;&gt;"dataset", "—", IFERROR(INDEX(A6:A2500, COUNTA(A6:A2500)), "—"))</f>
+        <f>IF(VDV_STATUS&lt;&gt;"dataset", "—", IFERROR(INDEX(H6:H2500, COUNTA(H6:H2500)), "—"))</f>
         <v/>
       </c>
     </row>
@@ -816,11 +830,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" s="30">
         <f>IF(VDV_STATUS&lt;&gt;"dataset", VDV_STATUS, IFERROR(FILTER(VDV_B, VDV_A="gdp"), ""))</f>
         <v/>
       </c>
-      <c r="B6">
+      <c r="B6" s="30">
         <f>IFERROR(FILTER(VDV_C, VDV_A="gdp"), "")</f>
         <v/>
       </c>
@@ -828,7 +842,7 @@
         <f>IFERROR(ARRAYFORMULA(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(FILTER(VDV_D, VDV_A="gdp"), "agriculture", "Nông-lâm-thủy sản"), "industry", "Công nghiệp-xây dựng"), "services", "Dịch vụ"), "total", "Toàn nền kinh tế")), "")</f>
         <v/>
       </c>
-      <c r="D6">
+      <c r="D6" s="27">
         <f>IFERROR(FILTER(VDV_F, VDV_A="gdp"), "")</f>
         <v/>
       </c>
@@ -918,23 +932,23 @@
         <f>IF(VDV_STATUS&lt;&gt;"dataset", VDV_STATUS, IFERROR(ARRAYFORMULA(TEXT(FILTER(VDV_B, VDV_A="trade"), "yyyy-mm")), ""))</f>
         <v/>
       </c>
-      <c r="B6">
+      <c r="B6" s="27">
         <f>IFERROR(FILTER(VDV_C, VDV_A="trade"), "")</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C6" s="27">
         <f>IFERROR(FILTER(VDV_D, VDV_A="trade"), "")</f>
         <v/>
       </c>
-      <c r="D6">
+      <c r="D6" s="27">
         <f>IFERROR(FILTER(VDV_E, VDV_A="trade"), "")</f>
         <v/>
       </c>
-      <c r="E6">
+      <c r="E6" s="32">
         <f>IFERROR(FILTER(VDV_F, VDV_A="trade"), "")</f>
         <v/>
       </c>
-      <c r="F6">
+      <c r="F6" s="32">
         <f>IFERROR(FILTER(VDV_G, VDV_A="trade"), "")</f>
         <v/>
       </c>
@@ -1782,11 +1796,11 @@
         <f>IF(VDV_STATUS&lt;&gt;"dataset", VDV_STATUS, IFERROR(ARRAYFORMULA(TEXT(FILTER(VDV_B, VDV_A="gold"), "yyyy-mm-dd")), ""))</f>
         <v/>
       </c>
-      <c r="B6">
+      <c r="B6" s="23">
         <f>IFERROR(FILTER(VDV_C, VDV_A="gold"), "")</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C6" s="23">
         <f>IFERROR(FILTER(VDV_D, VDV_A="gold"), "")</f>
         <v/>
       </c>
@@ -1850,11 +1864,11 @@
         <f>IF(VDV_STATUS&lt;&gt;"dataset", VDV_STATUS, IFERROR(ARRAYFORMULA(TEXT(FILTER(VDV_B, VDV_A="silver"), "yyyy-mm-dd")), ""))</f>
         <v/>
       </c>
-      <c r="B6">
+      <c r="B6" s="23">
         <f>IFERROR(FILTER(VDV_C, VDV_A="silver"), "")</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C6" s="23">
         <f>IFERROR(FILTER(VDV_D, VDV_A="silver"), "")</f>
         <v/>
       </c>
@@ -1948,31 +1962,31 @@
         <f>IF(VDV_STATUS&lt;&gt;"dataset", VDV_STATUS, IFERROR(ARRAYFORMULA(TEXT(FILTER(VDV_B, VDV_A="interbank"), "yyyy-mm-dd")), ""))</f>
         <v/>
       </c>
-      <c r="B6">
+      <c r="B6" s="27">
         <f>IFERROR(FILTER(VDV_C, VDV_A="interbank"), "")</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C6" s="27">
         <f>IFERROR(FILTER(VDV_D, VDV_A="interbank"), "")</f>
         <v/>
       </c>
-      <c r="D6">
+      <c r="D6" s="27">
         <f>IFERROR(FILTER(VDV_E, VDV_A="interbank"), "")</f>
         <v/>
       </c>
-      <c r="E6">
+      <c r="E6" s="27">
         <f>IFERROR(FILTER(VDV_F, VDV_A="interbank"), "")</f>
         <v/>
       </c>
-      <c r="F6">
+      <c r="F6" s="27">
         <f>IFERROR(FILTER(VDV_G, VDV_A="interbank"), "")</f>
         <v/>
       </c>
-      <c r="G6">
+      <c r="G6" s="27">
         <f>IFERROR(FILTER(VDV_H, VDV_A="interbank"), "")</f>
         <v/>
       </c>
-      <c r="H6">
+      <c r="H6" s="27">
         <f>IFERROR(FILTER(VDV_I, VDV_A="interbank"), "")</f>
         <v/>
       </c>
@@ -2030,7 +2044,7 @@
         <f>IF(VDV_STATUS&lt;&gt;"dataset", VDV_STATUS, IFERROR(ARRAYFORMULA(TEXT(FILTER(VDV_B, VDV_A="fx"), "yyyy-mm-dd")), ""))</f>
         <v/>
       </c>
-      <c r="B6">
+      <c r="B6" s="23">
         <f>IFERROR(FILTER(VDV_C, VDV_A="fx"), "")</f>
         <v/>
       </c>
@@ -2112,23 +2126,23 @@
         <f>IF(VDV_STATUS&lt;&gt;"dataset", VDV_STATUS, IFERROR(ARRAYFORMULA(TEXT(FILTER(VDV_B, VDV_A="deposit"), "yyyy-mm-dd")), ""))</f>
         <v/>
       </c>
-      <c r="B6">
+      <c r="B6" s="27">
         <f>IFERROR(FILTER(VDV_C, VDV_A="deposit"), "")</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C6" s="27">
         <f>IFERROR(FILTER(VDV_D, VDV_A="deposit"), "")</f>
         <v/>
       </c>
-      <c r="D6">
+      <c r="D6" s="27">
         <f>IFERROR(FILTER(VDV_E, VDV_A="deposit"), "")</f>
         <v/>
       </c>
-      <c r="E6">
+      <c r="E6" s="27">
         <f>IFERROR(FILTER(VDV_F, VDV_A="deposit"), "")</f>
         <v/>
       </c>
-      <c r="F6">
+      <c r="F6" s="27">
         <f>IFERROR(FILTER(VDV_G, VDV_A="deposit"), "")</f>
         <v/>
       </c>
@@ -2198,15 +2212,15 @@
         <f>IF(VDV_STATUS&lt;&gt;"dataset", VDV_STATUS, IFERROR(ARRAYFORMULA(TEXT(FILTER(VDV_B, VDV_A="global"), "yyyy-mm-dd")), ""))</f>
         <v/>
       </c>
-      <c r="B6">
+      <c r="B6" s="28">
         <f>IFERROR(FILTER(VDV_C, VDV_A="global"), "")</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C6" s="29">
         <f>IFERROR(FILTER(VDV_D, VDV_A="global"), "")</f>
         <v/>
       </c>
-      <c r="D6">
+      <c r="D6" s="23">
         <f>IFERROR(FILTER(VDV_E, VDV_A="global"), "")</f>
         <v/>
       </c>
@@ -2270,11 +2284,11 @@
         <f>IF(VDV_STATUS&lt;&gt;"dataset", VDV_STATUS, IFERROR(ARRAYFORMULA(TEXT(FILTER(VDV_B, VDV_A="cpi"), "yyyy-mm")), ""))</f>
         <v/>
       </c>
-      <c r="B6">
+      <c r="B6" s="27">
         <f>IFERROR(FILTER(VDV_C, VDV_A="cpi"), "")</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C6" s="27">
         <f>IFERROR(FILTER(VDV_D, VDV_A="cpi"), "")</f>
         <v/>
       </c>
